--- a/output/roomself_excel/9686.xlsx
+++ b/output/roomself_excel/9686.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>698155</v>
+        <v>156799</v>
       </c>
       <c r="D2" t="n">
-        <v>12332</v>
+        <v>3176</v>
       </c>
       <c r="E2" t="n">
-        <v>1043</v>
+        <v>395</v>
       </c>
       <c r="F2" t="n">
-        <v>1019</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>48267</v>
+        <v>380620</v>
       </c>
       <c r="D3" t="n">
-        <v>1808</v>
+        <v>6444</v>
       </c>
       <c r="E3" t="n">
-        <v>343</v>
+        <v>1043</v>
       </c>
       <c r="F3" t="n">
-        <v>202</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>126597</v>
+        <v>108528</v>
       </c>
       <c r="D4" t="n">
-        <v>4120</v>
+        <v>2684</v>
       </c>
       <c r="E4" t="n">
-        <v>499</v>
+        <v>312</v>
       </c>
       <c r="F4" t="n">
-        <v>366</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>174270</v>
+        <v>116907</v>
       </c>
       <c r="D5" t="n">
-        <v>3364</v>
+        <v>2768</v>
       </c>
       <c r="E5" t="n">
-        <v>487</v>
+        <v>293</v>
       </c>
       <c r="F5" t="n">
-        <v>386</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>108528</v>
+        <v>134664</v>
       </c>
       <c r="D6" t="n">
-        <v>2684</v>
+        <v>2936</v>
       </c>
       <c r="E6" t="n">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F6" t="n">
-        <v>309</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34704</v>
+        <v>94928</v>
       </c>
       <c r="D7" t="n">
-        <v>1540</v>
+        <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>156</v>
+        <v>377</v>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>162959</v>
+        <v>108528</v>
       </c>
       <c r="D8" t="n">
-        <v>4676</v>
+        <v>2684</v>
       </c>
       <c r="E8" t="n">
-        <v>548</v>
+        <v>422</v>
       </c>
       <c r="F8" t="n">
-        <v>447</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38665</v>
+        <v>126597</v>
       </c>
       <c r="D9" t="n">
-        <v>1720</v>
+        <v>4120</v>
       </c>
       <c r="E9" t="n">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="F9" t="n">
-        <v>158</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>116907</v>
+        <v>38665</v>
       </c>
       <c r="D10" t="n">
-        <v>2768</v>
+        <v>1720</v>
       </c>
       <c r="E10" t="n">
-        <v>293</v>
+        <v>183</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>134664</v>
+        <v>36720</v>
       </c>
       <c r="D11" t="n">
-        <v>2936</v>
+        <v>1544</v>
       </c>
       <c r="E11" t="n">
-        <v>411</v>
+        <v>163</v>
       </c>
       <c r="F11" t="n">
-        <v>379</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>36720</v>
+        <v>160736</v>
       </c>
       <c r="D12" t="n">
-        <v>1544</v>
+        <v>5364</v>
       </c>
       <c r="E12" t="n">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
-        <v>163</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>94928</v>
+        <v>34704</v>
       </c>
       <c r="D13" t="n">
-        <v>2484</v>
+        <v>1540</v>
       </c>
       <c r="E13" t="n">
-        <v>377</v>
+        <v>156</v>
       </c>
       <c r="F13" t="n">
-        <v>304</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>76298</v>
+        <v>48267</v>
       </c>
       <c r="D14" t="n">
-        <v>2436</v>
+        <v>1808</v>
       </c>
       <c r="E14" t="n">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="F14" t="n">
-        <v>280</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>108528</v>
+        <v>174270</v>
       </c>
       <c r="D15" t="n">
-        <v>2684</v>
+        <v>3364</v>
       </c>
       <c r="E15" t="n">
-        <v>599</v>
+        <v>487</v>
       </c>
       <c r="F15" t="n">
-        <v>288</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16">
@@ -778,15 +778,59 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>162959</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4676</v>
+      </c>
+      <c r="E16" t="n">
+        <v>374</v>
+      </c>
+      <c r="F16" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>76298</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2436</v>
+      </c>
+      <c r="E17" t="n">
+        <v>375</v>
+      </c>
+      <c r="F17" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>18753</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D18" t="n">
         <v>1096</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E18" t="n">
         <v>141</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
         <v>16</v>
       </c>
     </row>

--- a/output/roomself_excel/9686.xlsx
+++ b/output/roomself_excel/9686.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,37 @@
       <c r="D2" t="n">
         <v>3176</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>395</v>
       </c>
-      <c r="F2" t="n">
-        <v>16</v>
-      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>399</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +587,60 @@
       <c r="D3" t="n">
         <v>6444</v>
       </c>
-      <c r="E3" t="n">
-        <v>1043</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>624</v>
+        <v>295</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>478</v>
+      </c>
+      <c r="J3" t="n">
+        <v>46</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>181</v>
+      </c>
+      <c r="M3" t="n">
+        <v>16</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>242</v>
+      </c>
+      <c r="P3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>493</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +658,37 @@
       <c r="D4" t="n">
         <v>2684</v>
       </c>
-      <c r="E4" t="n">
-        <v>312</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>267</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>272</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +705,29 @@
       <c r="D5" t="n">
         <v>2768</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>293</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>23</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +744,45 @@
       <c r="D6" t="n">
         <v>2936</v>
       </c>
-      <c r="E6" t="n">
-        <v>411</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>379</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>131</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>372</v>
+      </c>
+      <c r="M6" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +799,45 @@
       <c r="D7" t="n">
         <v>2484</v>
       </c>
-      <c r="E7" t="n">
-        <v>377</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>304</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>467</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>272</v>
+      </c>
+      <c r="M7" t="n">
+        <v>16</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +854,37 @@
       <c r="D8" t="n">
         <v>2684</v>
       </c>
-      <c r="E8" t="n">
-        <v>422</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>288</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>399</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +901,37 @@
       <c r="D9" t="n">
         <v>4120</v>
       </c>
-      <c r="E9" t="n">
-        <v>366</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>294</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>263</v>
+      </c>
+      <c r="J9" t="n">
+        <v>42</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +948,37 @@
       <c r="D10" t="n">
         <v>1720</v>
       </c>
-      <c r="E10" t="n">
-        <v>183</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>158</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>142</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +995,29 @@
       <c r="D11" t="n">
         <v>1544</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>163</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>15</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +1034,29 @@
       <c r="D12" t="n">
         <v>5364</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>143</v>
       </c>
-      <c r="F12" t="n">
-        <v>16</v>
-      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1073,45 @@
       <c r="D13" t="n">
         <v>1540</v>
       </c>
-      <c r="E13" t="n">
-        <v>156</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>59</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>13</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>141</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1128,45 @@
       <c r="D14" t="n">
         <v>1808</v>
       </c>
-      <c r="E14" t="n">
-        <v>343</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>202</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="G14" t="n">
+        <v>29</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>173</v>
+      </c>
+      <c r="J14" t="n">
+        <v>47</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>173</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1183,37 @@
       <c r="D15" t="n">
         <v>3364</v>
       </c>
-      <c r="E15" t="n">
-        <v>487</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>386</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>471</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1230,29 @@
       <c r="D16" t="n">
         <v>4676</v>
       </c>
-      <c r="E16" t="n">
-        <v>374</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>287</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="G16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1269,37 @@
       <c r="D17" t="n">
         <v>2436</v>
       </c>
-      <c r="E17" t="n">
-        <v>375</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>280</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>264</v>
+      </c>
+      <c r="J17" t="n">
+        <v>30</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1316,29 @@
       <c r="D18" t="n">
         <v>1096</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>141</v>
       </c>
-      <c r="F18" t="n">
-        <v>16</v>
-      </c>
+      <c r="G18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
